--- a/artfynd/S 145-2026 artfynd.xlsx
+++ b/artfynd/S 145-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ2"/>
+  <dimension ref="A1:AZ4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -680,56 +680,61 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>88194865</v>
+        <v>137217126</v>
       </c>
       <c r="B2" t="n">
-        <v>89908</v>
+        <v>100734</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1255</v>
+        <v>522</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Borstskölding</t>
+          <t>Sjötåtel</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Pluteus umbrosus</t>
+          <t>Deschampsia setacea</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Pers. : Fr.) P. Kumm.</t>
+          <t>(Huds.) Hack.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr"/>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>i frukt</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Lilla Stenbrohult, Sm</t>
+          <t>Stenbrohults prästgård, Kyrkvikens strand, Stenbrohult, Sm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>449059</v>
+        <v>449085</v>
       </c>
       <c r="R2" t="n">
-        <v>6274547</v>
+        <v>6274579</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -756,17 +761,27 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2020-09-26</t>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="Z2" t="inlineStr">
+        <is>
+          <t>11:20</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2020-09-26</t>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="AB2" t="inlineStr">
+        <is>
+          <t>13:30</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>bokområde med äldre bokar, grov boklåga</t>
+          <t>en stor blommande tuva, ny fyndplats</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -793,13 +808,268 @@
       <c r="AY2" t="inlineStr"/>
       <c r="AZ2" t="inlineStr">
         <is>
+          <t>https://artportalen.se/Sighting/137217126</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>88194865</v>
+      </c>
+      <c r="B3" t="n">
+        <v>89908</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>1255</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Borstskölding</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Pluteus umbrosus</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>(Pers. : Fr.) P. Kumm.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr"/>
+      <c r="N3" t="inlineStr"/>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Lilla Stenbrohult, Sm</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>449059</v>
+      </c>
+      <c r="R3" t="n">
+        <v>6274547</v>
+      </c>
+      <c r="S3" t="n">
+        <v>10</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Kronoberg</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Älmhult</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Stenbrohult</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2020-09-26</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2020-09-26</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>bokområde med äldre bokar, grov boklåga</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF3" t="inlineStr"/>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>Sven G Nilsson</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Sven G Nilsson</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
           <t>https://artportalen.se/Sighting/88194865</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>137218025</v>
+      </c>
+      <c r="B4" t="n">
+        <v>98327</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>222593</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Safsa</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Osmunda regalis</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Möckelns strand, Lilla Stenbrohult, Sm</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>449031</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6274544</v>
+      </c>
+      <c r="S4" t="n">
+        <v>10</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Kronoberg</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Älmhult</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Stenbrohult</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>11:20</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>13:30</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>litet ex på stranden</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF4" t="inlineStr"/>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Sven G Nilsson</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Sven G Nilsson</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137218025</t>
         </is>
       </c>
     </row>
   </sheetData>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/S 145-2026 artfynd.xlsx
+++ b/artfynd/S 145-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137217126</v>
       </c>
       <c r="B2" t="n">
-        <v>100734</v>
+        <v>100747</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -936,7 +936,7 @@
         <v>137218025</v>
       </c>
       <c r="B4" t="n">
-        <v>98327</v>
+        <v>98340</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/S 145-2026 artfynd.xlsx
+++ b/artfynd/S 145-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137217126</v>
       </c>
       <c r="B2" t="n">
-        <v>100747</v>
+        <v>100749</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -936,7 +936,7 @@
         <v>137218025</v>
       </c>
       <c r="B4" t="n">
-        <v>98340</v>
+        <v>98342</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/S 145-2026 artfynd.xlsx
+++ b/artfynd/S 145-2026 artfynd.xlsx
@@ -718,11 +718,7 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>i frukt</t>
-        </is>
-      </c>
+      <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
@@ -971,11 +967,7 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+      <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">

--- a/artfynd/S 145-2026 artfynd.xlsx
+++ b/artfynd/S 145-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137217126</v>
       </c>
       <c r="B2" t="n">
-        <v>100749</v>
+        <v>100752</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -932,7 +932,7 @@
         <v>137218025</v>
       </c>
       <c r="B4" t="n">
-        <v>98342</v>
+        <v>98345</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/S 145-2026 artfynd.xlsx
+++ b/artfynd/S 145-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137217126</v>
       </c>
       <c r="B2" t="n">
-        <v>100752</v>
+        <v>100762</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -932,7 +932,7 @@
         <v>137218025</v>
       </c>
       <c r="B4" t="n">
-        <v>98345</v>
+        <v>98355</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/S 145-2026 artfynd.xlsx
+++ b/artfynd/S 145-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137217126</v>
       </c>
       <c r="B2" t="n">
-        <v>100762</v>
+        <v>100763</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -932,7 +932,7 @@
         <v>137218025</v>
       </c>
       <c r="B4" t="n">
-        <v>98355</v>
+        <v>98356</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/S 145-2026 artfynd.xlsx
+++ b/artfynd/S 145-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137217126</v>
       </c>
       <c r="B2" t="n">
-        <v>100763</v>
+        <v>100768</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -932,7 +932,7 @@
         <v>137218025</v>
       </c>
       <c r="B4" t="n">
-        <v>98356</v>
+        <v>98361</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/S 145-2026 artfynd.xlsx
+++ b/artfynd/S 145-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137217126</v>
       </c>
       <c r="B2" t="n">
-        <v>100768</v>
+        <v>100771</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -932,7 +932,7 @@
         <v>137218025</v>
       </c>
       <c r="B4" t="n">
-        <v>98361</v>
+        <v>98363</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/S 145-2026 artfynd.xlsx
+++ b/artfynd/S 145-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137217126</v>
       </c>
       <c r="B2" t="n">
-        <v>100771</v>
+        <v>100777</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -932,7 +932,7 @@
         <v>137218025</v>
       </c>
       <c r="B4" t="n">
-        <v>98363</v>
+        <v>98369</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/S 145-2026 artfynd.xlsx
+++ b/artfynd/S 145-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137217126</v>
       </c>
       <c r="B2" t="n">
-        <v>100777</v>
+        <v>100789</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -932,7 +932,7 @@
         <v>137218025</v>
       </c>
       <c r="B4" t="n">
-        <v>98369</v>
+        <v>98381</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/S 145-2026 artfynd.xlsx
+++ b/artfynd/S 145-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137217126</v>
       </c>
       <c r="B2" t="n">
-        <v>100789</v>
+        <v>100790</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -932,7 +932,7 @@
         <v>137218025</v>
       </c>
       <c r="B4" t="n">
-        <v>98381</v>
+        <v>98382</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/S 145-2026 artfynd.xlsx
+++ b/artfynd/S 145-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137217126</v>
       </c>
       <c r="B2" t="n">
-        <v>100790</v>
+        <v>100793</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -932,7 +932,7 @@
         <v>137218025</v>
       </c>
       <c r="B4" t="n">
-        <v>98382</v>
+        <v>98385</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/S 145-2026 artfynd.xlsx
+++ b/artfynd/S 145-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137217126</v>
       </c>
       <c r="B2" t="n">
-        <v>100793</v>
+        <v>100797</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -932,7 +932,7 @@
         <v>137218025</v>
       </c>
       <c r="B4" t="n">
-        <v>98385</v>
+        <v>98389</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
